--- a/product_selector_out/STM32U595-5A5.xlsx
+++ b/product_selector_out/STM32U595-5A5.xlsx
@@ -61,12 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5892,7 +5892,7 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6837,9 +6837,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -6852,17 +6852,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J12" s="8" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6877,7 +6877,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="M12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6887,29 +6887,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R12" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S12" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T12" s="6" t="inlineStr">
@@ -6937,12 +6937,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z12" s="8" t="inlineStr">
+      <c r="Y12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6967,7 +6967,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE12" s="8" t="inlineStr">
+      <c r="AE12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6977,7 +6977,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG12" s="8" t="inlineStr">
+      <c r="AG12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6987,7 +6987,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI12" s="8" t="inlineStr">
+      <c r="AI12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6997,7 +6997,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK12" s="8" t="inlineStr">
+      <c r="AK12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7017,7 +7017,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO12" s="8" t="inlineStr">
+      <c r="AO12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7042,12 +7042,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU12" s="8" t="inlineStr">
+      <c r="AT12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7057,19 +7057,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW12" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY12" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ12" s="6" t="inlineStr">
@@ -7087,42 +7087,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ12" s="8" t="inlineStr">
+      <c r="BC12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7137,9 +7137,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -7164,7 +7164,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -7179,17 +7179,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J13" s="8" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7204,7 +7204,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M13" s="8" t="inlineStr">
+      <c r="M13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7214,17 +7214,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q13" s="8" t="inlineStr">
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7264,12 +7264,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z13" s="8" t="inlineStr">
+      <c r="Y13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7294,7 +7294,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE13" s="8" t="inlineStr">
+      <c r="AE13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7304,7 +7304,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG13" s="8" t="inlineStr">
+      <c r="AG13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7314,7 +7314,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI13" s="8" t="inlineStr">
+      <c r="AI13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7324,7 +7324,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK13" s="8" t="inlineStr">
+      <c r="AK13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7344,12 +7344,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP13" s="8" t="inlineStr">
+      <c r="AO13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7369,12 +7369,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU13" s="8" t="inlineStr">
+      <c r="AT13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7389,9 +7389,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY13" s="9" t="inlineStr">
@@ -7414,42 +7414,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ13" s="8" t="inlineStr">
+      <c r="BC13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7491,7 +7491,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -7506,17 +7506,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J14" s="8" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7531,7 +7531,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M14" s="8" t="inlineStr">
+      <c r="M14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7541,17 +7541,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q14" s="8" t="inlineStr">
+      <c r="O14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7591,12 +7591,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z14" s="8" t="inlineStr">
+      <c r="Y14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7621,7 +7621,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE14" s="8" t="inlineStr">
+      <c r="AE14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7631,7 +7631,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG14" s="8" t="inlineStr">
+      <c r="AG14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7641,7 +7641,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI14" s="8" t="inlineStr">
+      <c r="AI14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7651,7 +7651,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK14" s="8" t="inlineStr">
+      <c r="AK14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7671,12 +7671,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP14" s="8" t="inlineStr">
+      <c r="AO14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7696,12 +7696,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU14" s="8" t="inlineStr">
+      <c r="AT14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7716,9 +7716,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY14" s="9" t="inlineStr">
@@ -7741,42 +7741,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ14" s="8" t="inlineStr">
+      <c r="BC14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7818,9 +7818,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -7833,17 +7833,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J15" s="8" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7858,7 +7858,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M15" s="8" t="inlineStr">
+      <c r="M15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7868,29 +7868,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T15" s="6" t="inlineStr">
@@ -7918,12 +7918,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z15" s="8" t="inlineStr">
+      <c r="Y15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7948,7 +7948,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE15" s="8" t="inlineStr">
+      <c r="AE15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7958,7 +7958,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG15" s="8" t="inlineStr">
+      <c r="AG15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7968,7 +7968,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI15" s="8" t="inlineStr">
+      <c r="AI15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7978,7 +7978,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK15" s="8" t="inlineStr">
+      <c r="AK15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7998,7 +7998,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO15" s="8" t="inlineStr">
+      <c r="AO15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8023,12 +8023,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU15" s="8" t="inlineStr">
+      <c r="AT15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8038,19 +8038,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ15" s="6" t="inlineStr">
@@ -8068,42 +8068,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ15" s="8" t="inlineStr">
+      <c r="BC15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8118,9 +8118,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8145,7 +8145,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -8160,17 +8160,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J16" s="8" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8185,7 +8185,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M16" s="8" t="inlineStr">
+      <c r="M16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8195,17 +8195,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q16" s="8" t="inlineStr">
+      <c r="O16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8245,12 +8245,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z16" s="8" t="inlineStr">
+      <c r="Y16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8275,7 +8275,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE16" s="8" t="inlineStr">
+      <c r="AE16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8285,7 +8285,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG16" s="8" t="inlineStr">
+      <c r="AG16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8295,7 +8295,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI16" s="8" t="inlineStr">
+      <c r="AI16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8305,7 +8305,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK16" s="8" t="inlineStr">
+      <c r="AK16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8325,12 +8325,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP16" s="8" t="inlineStr">
+      <c r="AO16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8350,12 +8350,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU16" s="8" t="inlineStr">
+      <c r="AT16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8370,9 +8370,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY16" s="9" t="inlineStr">
@@ -8395,42 +8395,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ16" s="8" t="inlineStr">
+      <c r="BC16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8472,7 +8472,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -8487,17 +8487,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J17" s="8" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8512,7 +8512,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M17" s="8" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8522,17 +8522,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q17" s="8" t="inlineStr">
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8572,12 +8572,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z17" s="8" t="inlineStr">
+      <c r="Y17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8602,7 +8602,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE17" s="8" t="inlineStr">
+      <c r="AE17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8612,7 +8612,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG17" s="8" t="inlineStr">
+      <c r="AG17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8622,7 +8622,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI17" s="8" t="inlineStr">
+      <c r="AI17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8632,7 +8632,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK17" s="8" t="inlineStr">
+      <c r="AK17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8652,12 +8652,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP17" s="8" t="inlineStr">
+      <c r="AO17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8677,12 +8677,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU17" s="8" t="inlineStr">
+      <c r="AT17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8697,9 +8697,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY17" s="9" t="inlineStr">
@@ -8722,42 +8722,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ17" s="8" t="inlineStr">
+      <c r="BC17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8799,7 +8799,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -8814,17 +8814,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J18" s="8" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8839,7 +8839,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M18" s="8" t="inlineStr">
+      <c r="M18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8849,17 +8849,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q18" s="8" t="inlineStr">
+      <c r="O18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8899,12 +8899,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z18" s="8" t="inlineStr">
+      <c r="Y18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8919,7 +8919,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC18" s="8" t="inlineStr">
+      <c r="AC18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8929,7 +8929,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE18" s="8" t="inlineStr">
+      <c r="AE18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8939,7 +8939,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG18" s="8" t="inlineStr">
+      <c r="AG18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8949,7 +8949,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI18" s="8" t="inlineStr">
+      <c r="AI18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8959,7 +8959,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK18" s="8" t="inlineStr">
+      <c r="AK18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8979,12 +8979,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP18" s="8" t="inlineStr">
+      <c r="AO18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9004,12 +9004,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU18" s="8" t="inlineStr">
+      <c r="AT18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9024,9 +9024,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY18" s="9" t="inlineStr">
@@ -9049,42 +9049,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ18" s="8" t="inlineStr">
+      <c r="BC18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9126,7 +9126,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -9141,17 +9141,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9166,7 +9166,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M19" s="8" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9176,17 +9176,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q19" s="8" t="inlineStr">
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9226,12 +9226,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z19" s="8" t="inlineStr">
+      <c r="Y19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9256,7 +9256,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE19" s="8" t="inlineStr">
+      <c r="AE19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9266,7 +9266,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG19" s="8" t="inlineStr">
+      <c r="AG19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9276,7 +9276,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI19" s="8" t="inlineStr">
+      <c r="AI19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9286,7 +9286,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK19" s="8" t="inlineStr">
+      <c r="AK19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9331,12 +9331,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU19" s="8" t="inlineStr">
+      <c r="AT19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9351,9 +9351,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY19" s="9" t="inlineStr">
@@ -9376,42 +9376,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ19" s="8" t="inlineStr">
+      <c r="BC19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9453,9 +9453,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -9468,17 +9468,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9493,7 +9493,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M20" s="8" t="inlineStr">
+      <c r="M20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9503,12 +9503,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P20" s="8" t="inlineStr">
+      <c r="O20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9518,14 +9518,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R20" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S20" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T20" s="6" t="inlineStr">
@@ -9553,12 +9553,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z20" s="8" t="inlineStr">
+      <c r="Y20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9583,7 +9583,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE20" s="8" t="inlineStr">
+      <c r="AE20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9593,7 +9593,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG20" s="8" t="inlineStr">
+      <c r="AG20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9603,7 +9603,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI20" s="8" t="inlineStr">
+      <c r="AI20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9613,7 +9613,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK20" s="8" t="inlineStr">
+      <c r="AK20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9633,7 +9633,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO20" s="8" t="inlineStr">
+      <c r="AO20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9658,12 +9658,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU20" s="8" t="inlineStr">
+      <c r="AT20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9673,19 +9673,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW20" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY20" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ20" s="6" t="inlineStr">
@@ -9703,42 +9703,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ20" s="8" t="inlineStr">
+      <c r="BC20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9753,9 +9753,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -9780,7 +9780,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -9795,17 +9795,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J21" s="8" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9820,7 +9820,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M21" s="8" t="inlineStr">
+      <c r="M21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9830,17 +9830,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q21" s="8" t="inlineStr">
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9880,12 +9880,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z21" s="8" t="inlineStr">
+      <c r="Y21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9910,7 +9910,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE21" s="8" t="inlineStr">
+      <c r="AE21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9920,7 +9920,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG21" s="8" t="inlineStr">
+      <c r="AG21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9930,7 +9930,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI21" s="8" t="inlineStr">
+      <c r="AI21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9940,7 +9940,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK21" s="8" t="inlineStr">
+      <c r="AK21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9960,12 +9960,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP21" s="8" t="inlineStr">
+      <c r="AO21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9985,12 +9985,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU21" s="8" t="inlineStr">
+      <c r="AT21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10005,9 +10005,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY21" s="9" t="inlineStr">
@@ -10030,42 +10030,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ21" s="8" t="inlineStr">
+      <c r="BC21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10107,9 +10107,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -10122,17 +10122,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J22" s="8" t="inlineStr">
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10147,7 +10147,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M22" s="8" t="inlineStr">
+      <c r="M22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10157,29 +10157,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R22" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S22" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T22" s="6" t="inlineStr">
@@ -10207,12 +10207,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z22" s="8" t="inlineStr">
+      <c r="Y22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10237,7 +10237,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE22" s="8" t="inlineStr">
+      <c r="AE22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10247,7 +10247,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG22" s="8" t="inlineStr">
+      <c r="AG22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10257,7 +10257,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI22" s="8" t="inlineStr">
+      <c r="AI22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10267,7 +10267,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK22" s="8" t="inlineStr">
+      <c r="AK22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10287,7 +10287,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO22" s="8" t="inlineStr">
+      <c r="AO22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10312,12 +10312,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU22" s="8" t="inlineStr">
+      <c r="AT22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10327,19 +10327,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW22" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY22" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ22" s="6" t="inlineStr">
@@ -10357,42 +10357,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ22" s="8" t="inlineStr">
+      <c r="BC22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10407,9 +10407,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -10434,7 +10434,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -10449,17 +10449,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J23" s="8" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10474,7 +10474,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M23" s="8" t="inlineStr">
+      <c r="M23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10484,17 +10484,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q23" s="8" t="inlineStr">
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10534,12 +10534,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z23" s="8" t="inlineStr">
+      <c r="Y23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10564,7 +10564,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE23" s="8" t="inlineStr">
+      <c r="AE23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10574,7 +10574,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG23" s="8" t="inlineStr">
+      <c r="AG23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10584,7 +10584,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI23" s="8" t="inlineStr">
+      <c r="AI23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10594,7 +10594,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK23" s="8" t="inlineStr">
+      <c r="AK23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10639,12 +10639,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU23" s="8" t="inlineStr">
+      <c r="AT23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10659,9 +10659,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX23" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY23" s="9" t="inlineStr">
@@ -10684,42 +10684,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ23" s="8" t="inlineStr">
+      <c r="BC23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10761,7 +10761,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -10776,17 +10776,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J24" s="8" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10801,7 +10801,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M24" s="8" t="inlineStr">
+      <c r="M24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10811,17 +10811,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q24" s="8" t="inlineStr">
+      <c r="O24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10861,12 +10861,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z24" s="8" t="inlineStr">
+      <c r="Y24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10891,7 +10891,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE24" s="8" t="inlineStr">
+      <c r="AE24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10901,7 +10901,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG24" s="8" t="inlineStr">
+      <c r="AG24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10911,7 +10911,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI24" s="8" t="inlineStr">
+      <c r="AI24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10921,7 +10921,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK24" s="8" t="inlineStr">
+      <c r="AK24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10941,12 +10941,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP24" s="8" t="inlineStr">
+      <c r="AO24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10966,12 +10966,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU24" s="8" t="inlineStr">
+      <c r="AT24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10986,9 +10986,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX24" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY24" s="9" t="inlineStr">
@@ -11011,42 +11011,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ24" s="8" t="inlineStr">
+      <c r="BC24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11088,7 +11088,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -11103,17 +11103,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J25" s="8" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11128,7 +11128,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M25" s="8" t="inlineStr">
+      <c r="M25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11138,17 +11138,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q25" s="8" t="inlineStr">
+      <c r="O25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11188,12 +11188,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z25" s="8" t="inlineStr">
+      <c r="Y25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11218,7 +11218,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE25" s="8" t="inlineStr">
+      <c r="AE25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11228,7 +11228,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG25" s="8" t="inlineStr">
+      <c r="AG25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11238,7 +11238,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI25" s="8" t="inlineStr">
+      <c r="AI25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11248,7 +11248,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK25" s="8" t="inlineStr">
+      <c r="AK25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11293,12 +11293,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU25" s="8" t="inlineStr">
+      <c r="AT25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11313,9 +11313,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX25" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY25" s="9" t="inlineStr">
@@ -11338,42 +11338,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ25" s="8" t="inlineStr">
+      <c r="BC25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11415,9 +11415,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -11430,17 +11430,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J26" s="8" t="inlineStr">
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11455,7 +11455,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M26" s="8" t="inlineStr">
+      <c r="M26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11465,29 +11465,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R26" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S26" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T26" s="6" t="inlineStr">
@@ -11515,12 +11515,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z26" s="8" t="inlineStr">
+      <c r="Y26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11545,7 +11545,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE26" s="8" t="inlineStr">
+      <c r="AE26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11555,7 +11555,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG26" s="8" t="inlineStr">
+      <c r="AG26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11565,7 +11565,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI26" s="8" t="inlineStr">
+      <c r="AI26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11575,7 +11575,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK26" s="8" t="inlineStr">
+      <c r="AK26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11595,7 +11595,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO26" s="8" t="inlineStr">
+      <c r="AO26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11620,12 +11620,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU26" s="8" t="inlineStr">
+      <c r="AT26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11635,19 +11635,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW26" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY26" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ26" s="6" t="inlineStr">
@@ -11665,42 +11665,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ26" s="8" t="inlineStr">
+      <c r="BC26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11715,9 +11715,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -11742,7 +11742,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -11757,17 +11757,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J27" s="8" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11782,7 +11782,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M27" s="8" t="inlineStr">
+      <c r="M27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11792,17 +11792,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q27" s="8" t="inlineStr">
+      <c r="O27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11842,12 +11842,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z27" s="8" t="inlineStr">
+      <c r="Y27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11872,7 +11872,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE27" s="8" t="inlineStr">
+      <c r="AE27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11882,7 +11882,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG27" s="8" t="inlineStr">
+      <c r="AG27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11892,7 +11892,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI27" s="8" t="inlineStr">
+      <c r="AI27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11902,7 +11902,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK27" s="8" t="inlineStr">
+      <c r="AK27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11922,12 +11922,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP27" s="8" t="inlineStr">
+      <c r="AO27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11947,12 +11947,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU27" s="8" t="inlineStr">
+      <c r="AT27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11967,9 +11967,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX27" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX27" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY27" s="9" t="inlineStr">
@@ -11992,42 +11992,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ27" s="8" t="inlineStr">
+      <c r="BC27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12063,7 +12063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12097,7 +12097,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>STM32U5A5VJ</t>
+          <t>STM32U595ZJ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -12112,14 +12112,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STM32U5A5VJ</t>
+          <t>STM32U595ZJ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -12134,14 +12134,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STM32U5A5VJ</t>
+          <t>STM32U595ZJ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -12156,19 +12156,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STM32U5A5VJ</t>
+          <t>STM32U595ZJ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -12178,7 +12178,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Table 65. Typical dynamic current consumption of peripherals</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
@@ -12190,7 +12190,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -12200,19 +12200,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STM32U595ZJ</t>
+          <t>STM32U595QJ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -12229,12 +12229,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STM32U595ZJ</t>
+          <t>STM32U595QJ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -12244,19 +12244,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM32U595ZJ</t>
+          <t>STM32U595QJ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -12278,7 +12278,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -12288,7 +12288,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
@@ -12300,7 +12300,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -12310,19 +12310,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STM32U595QJ</t>
+          <t>STM32U595QI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -12332,19 +12332,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32U595QJ</t>
+          <t>STM32U595QI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -12354,19 +12354,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32U5A5QJ</t>
+          <t>STM32U595QI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -12376,19 +12376,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32U5A5QJ</t>
+          <t>STM32U595QI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -12398,19 +12398,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32U5A5QJ</t>
+          <t>STM32U595QI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -12420,19 +12420,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32U5A5QJ</t>
+          <t>STM32U595VI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -12442,19 +12442,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Table 65. Typical dynamic current consumption of peripherals</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32U595QI</t>
+          <t>STM32U595VI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -12471,12 +12471,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32U595QI</t>
+          <t>STM32U595VI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -12486,19 +12486,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32U595QI</t>
+          <t>STM32U595VI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -12508,14 +12508,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32U595QI</t>
+          <t>STM32U595VI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -12537,7 +12537,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32U595VI</t>
+          <t>STM32U595RI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -12559,7 +12559,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32U595VI</t>
+          <t>STM32U595RI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -12581,7 +12581,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32U595VI</t>
+          <t>STM32U595RI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -12596,19 +12596,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32U595VI</t>
+          <t>STM32U595RI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -12618,7 +12618,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -12640,19 +12640,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32U595RI</t>
+          <t>STM32U595VJ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -12669,12 +12669,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32U595RI</t>
+          <t>STM32U595VJ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -12684,19 +12684,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32U595RI</t>
+          <t>STM32U595VJ</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -12706,7 +12706,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -12718,7 +12718,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -12728,7 +12728,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
@@ -12740,7 +12740,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -12750,19 +12750,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32U595VJ</t>
+          <t>STM32U595AI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -12772,19 +12772,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32U595VJ</t>
+          <t>STM32U595AI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -12794,19 +12794,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32U5A5ZJ</t>
+          <t>STM32U595AI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -12816,19 +12816,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32U5A5ZJ</t>
+          <t>STM32U595AI</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -12838,19 +12838,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32U5A5ZJ</t>
+          <t>STM32U595AI</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -12860,19 +12860,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32U5A5ZJ</t>
+          <t>STM32U595ZI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -12882,19 +12882,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Table 65. Typical dynamic current consumption of peripherals</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32U595AI</t>
+          <t>STM32U595ZI</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -12911,12 +12911,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32U595AI</t>
+          <t>STM32U595ZI</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -12926,19 +12926,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32U595AI</t>
+          <t>STM32U595ZI</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -12948,14 +12948,14 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32U595AI</t>
+          <t>STM32U595ZI</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -12977,7 +12977,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32U5A5QI</t>
+          <t>STM32U595RJ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -12992,14 +12992,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32U5A5QI</t>
+          <t>STM32U595RJ</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -13014,14 +13014,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32U5A5QI</t>
+          <t>STM32U595RJ</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -13036,19 +13036,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32U5A5QI</t>
+          <t>STM32U595RJ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -13058,19 +13058,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Table 65. Typical dynamic current consumption of peripherals</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32U595ZI</t>
+          <t>STM32U595RJ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -13080,19 +13080,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32U595ZI</t>
+          <t>STM32U5A5AJ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -13102,19 +13102,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32U595ZI</t>
+          <t>STM32U5A5AJ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -13124,19 +13124,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32U595ZI</t>
+          <t>STM32U5A5AJ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -13146,19 +13146,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32U595RJ</t>
+          <t>STM32U5A5AJ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -13168,19 +13168,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32U595RJ</t>
+          <t>STM32U5A5AJ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -13190,19 +13190,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 65. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32U595RJ</t>
+          <t>STM32U595AJ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -13212,19 +13212,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32U595RJ</t>
+          <t>STM32U595AJ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -13234,19 +13234,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32U5A5AJ</t>
+          <t>STM32U595AJ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -13256,19 +13256,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32U5A5AJ</t>
+          <t>STM32U595AJ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -13278,19 +13278,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32U5A5AJ</t>
+          <t>STM32U595AJ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -13299,204 +13299,6 @@
         </is>
       </c>
       <c r="D56" t="inlineStr">
-        <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>STM32U5A5AJ</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Table 65. Typical dynamic current consumption of peripherals</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>STM32U5A5RJ</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>STM32U5A5RJ</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>STM32U5A5RJ</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>STM32U5A5RJ</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Table 65. Typical dynamic current consumption of peripherals</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>STM32U595AJ</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>STM32U595AJ</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>STM32U595AJ</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>STM32U595AJ</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
         <is>
           <t>Table 64. Typical dynamic current consumption of peripherals</t>
         </is>

--- a/product_selector_out/STM32U595-5A5.xlsx
+++ b/product_selector_out/STM32U595-5A5.xlsx
@@ -61,12 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
         </is>
       </c>
     </row>
@@ -5892,7 +5892,7 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
         </is>
       </c>
     </row>
@@ -6837,9 +6837,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -6852,17 +6852,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6877,7 +6877,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M12" s="7" t="inlineStr">
+      <c r="M12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6887,29 +6887,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T12" s="6" t="inlineStr">
@@ -6937,12 +6937,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z12" s="7" t="inlineStr">
+      <c r="Y12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6967,7 +6967,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE12" s="7" t="inlineStr">
+      <c r="AE12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6977,7 +6977,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG12" s="7" t="inlineStr">
+      <c r="AG12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6987,7 +6987,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI12" s="7" t="inlineStr">
+      <c r="AI12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6997,7 +6997,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK12" s="7" t="inlineStr">
+      <c r="AK12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7017,7 +7017,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO12" s="7" t="inlineStr">
+      <c r="AO12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7042,12 +7042,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU12" s="7" t="inlineStr">
+      <c r="AT12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7057,19 +7057,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ12" s="6" t="inlineStr">
@@ -7087,42 +7087,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ12" s="7" t="inlineStr">
+      <c r="BC12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7137,9 +7137,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -7164,7 +7164,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -7179,17 +7179,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7204,7 +7204,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M13" s="7" t="inlineStr">
+      <c r="M13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7214,17 +7214,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q13" s="7" t="inlineStr">
+      <c r="O13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7264,12 +7264,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z13" s="7" t="inlineStr">
+      <c r="Y13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7294,7 +7294,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE13" s="7" t="inlineStr">
+      <c r="AE13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7304,7 +7304,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG13" s="7" t="inlineStr">
+      <c r="AG13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7314,7 +7314,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI13" s="7" t="inlineStr">
+      <c r="AI13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7324,7 +7324,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK13" s="7" t="inlineStr">
+      <c r="AK13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7344,12 +7344,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP13" s="7" t="inlineStr">
+      <c r="AO13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7369,12 +7369,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU13" s="7" t="inlineStr">
+      <c r="AT13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7414,42 +7414,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ13" s="7" t="inlineStr">
+      <c r="BC13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7491,7 +7491,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -7506,17 +7506,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7531,7 +7531,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M14" s="7" t="inlineStr">
+      <c r="M14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7541,17 +7541,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q14" s="7" t="inlineStr">
+      <c r="O14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7591,12 +7591,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z14" s="7" t="inlineStr">
+      <c r="Y14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7621,7 +7621,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE14" s="7" t="inlineStr">
+      <c r="AE14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7631,7 +7631,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG14" s="7" t="inlineStr">
+      <c r="AG14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7641,7 +7641,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI14" s="7" t="inlineStr">
+      <c r="AI14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7651,7 +7651,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK14" s="7" t="inlineStr">
+      <c r="AK14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7671,12 +7671,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP14" s="7" t="inlineStr">
+      <c r="AO14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7696,12 +7696,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU14" s="7" t="inlineStr">
+      <c r="AT14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7741,42 +7741,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ14" s="7" t="inlineStr">
+      <c r="BC14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7818,9 +7818,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -7833,17 +7833,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7858,7 +7858,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M15" s="7" t="inlineStr">
+      <c r="M15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7868,29 +7868,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T15" s="6" t="inlineStr">
@@ -7918,12 +7918,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z15" s="7" t="inlineStr">
+      <c r="Y15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7948,7 +7948,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE15" s="7" t="inlineStr">
+      <c r="AE15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7958,7 +7958,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG15" s="7" t="inlineStr">
+      <c r="AG15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7968,7 +7968,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI15" s="7" t="inlineStr">
+      <c r="AI15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7978,7 +7978,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK15" s="7" t="inlineStr">
+      <c r="AK15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7998,7 +7998,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO15" s="7" t="inlineStr">
+      <c r="AO15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8023,12 +8023,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU15" s="7" t="inlineStr">
+      <c r="AT15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8038,19 +8038,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ15" s="6" t="inlineStr">
@@ -8068,42 +8068,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ15" s="7" t="inlineStr">
+      <c r="BC15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8118,9 +8118,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -8145,7 +8145,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -8160,17 +8160,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8185,7 +8185,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M16" s="7" t="inlineStr">
+      <c r="M16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8195,17 +8195,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q16" s="7" t="inlineStr">
+      <c r="O16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8245,12 +8245,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z16" s="7" t="inlineStr">
+      <c r="Y16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8275,7 +8275,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE16" s="7" t="inlineStr">
+      <c r="AE16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8285,7 +8285,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG16" s="7" t="inlineStr">
+      <c r="AG16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8295,7 +8295,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI16" s="7" t="inlineStr">
+      <c r="AI16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8305,7 +8305,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK16" s="7" t="inlineStr">
+      <c r="AK16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8325,12 +8325,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP16" s="7" t="inlineStr">
+      <c r="AO16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8350,12 +8350,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU16" s="7" t="inlineStr">
+      <c r="AT16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8395,42 +8395,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ16" s="7" t="inlineStr">
+      <c r="BC16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8472,7 +8472,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -8487,17 +8487,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8512,7 +8512,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M17" s="7" t="inlineStr">
+      <c r="M17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8522,17 +8522,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q17" s="7" t="inlineStr">
+      <c r="O17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8572,12 +8572,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z17" s="7" t="inlineStr">
+      <c r="Y17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8602,7 +8602,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE17" s="7" t="inlineStr">
+      <c r="AE17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8612,7 +8612,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG17" s="7" t="inlineStr">
+      <c r="AG17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8622,7 +8622,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI17" s="7" t="inlineStr">
+      <c r="AI17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8632,7 +8632,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK17" s="7" t="inlineStr">
+      <c r="AK17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8652,12 +8652,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP17" s="7" t="inlineStr">
+      <c r="AO17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8677,12 +8677,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU17" s="7" t="inlineStr">
+      <c r="AT17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8722,42 +8722,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ17" s="7" t="inlineStr">
+      <c r="BC17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8799,7 +8799,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -8814,17 +8814,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J18" s="7" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8839,7 +8839,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M18" s="7" t="inlineStr">
+      <c r="M18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8849,17 +8849,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q18" s="7" t="inlineStr">
+      <c r="O18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8899,12 +8899,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z18" s="7" t="inlineStr">
+      <c r="Y18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8919,7 +8919,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC18" s="7" t="inlineStr">
+      <c r="AC18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8929,7 +8929,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE18" s="7" t="inlineStr">
+      <c r="AE18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8939,7 +8939,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG18" s="7" t="inlineStr">
+      <c r="AG18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8949,7 +8949,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI18" s="7" t="inlineStr">
+      <c r="AI18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8959,7 +8959,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK18" s="7" t="inlineStr">
+      <c r="AK18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8979,12 +8979,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP18" s="7" t="inlineStr">
+      <c r="AO18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9004,12 +9004,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU18" s="7" t="inlineStr">
+      <c r="AT18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9049,42 +9049,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ18" s="7" t="inlineStr">
+      <c r="BC18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9126,7 +9126,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -9141,17 +9141,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9166,7 +9166,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M19" s="7" t="inlineStr">
+      <c r="M19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9176,17 +9176,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q19" s="7" t="inlineStr">
+      <c r="O19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9226,12 +9226,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z19" s="7" t="inlineStr">
+      <c r="Y19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9256,7 +9256,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE19" s="7" t="inlineStr">
+      <c r="AE19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9266,7 +9266,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG19" s="7" t="inlineStr">
+      <c r="AG19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9276,7 +9276,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI19" s="7" t="inlineStr">
+      <c r="AI19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9286,7 +9286,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK19" s="7" t="inlineStr">
+      <c r="AK19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9331,12 +9331,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU19" s="7" t="inlineStr">
+      <c r="AT19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9376,42 +9376,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ19" s="7" t="inlineStr">
+      <c r="BC19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9453,9 +9453,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -9468,17 +9468,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J20" s="7" t="inlineStr">
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9493,7 +9493,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M20" s="7" t="inlineStr">
+      <c r="M20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9503,12 +9503,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P20" s="7" t="inlineStr">
+      <c r="O20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9518,14 +9518,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T20" s="6" t="inlineStr">
@@ -9553,12 +9553,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z20" s="7" t="inlineStr">
+      <c r="Y20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9583,7 +9583,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE20" s="7" t="inlineStr">
+      <c r="AE20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9593,7 +9593,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG20" s="7" t="inlineStr">
+      <c r="AG20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9603,7 +9603,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI20" s="7" t="inlineStr">
+      <c r="AI20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9613,7 +9613,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK20" s="7" t="inlineStr">
+      <c r="AK20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9633,7 +9633,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO20" s="7" t="inlineStr">
+      <c r="AO20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9658,12 +9658,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU20" s="7" t="inlineStr">
+      <c r="AT20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9673,19 +9673,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ20" s="6" t="inlineStr">
@@ -9703,42 +9703,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ20" s="7" t="inlineStr">
+      <c r="BC20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9753,9 +9753,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -9780,7 +9780,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -9795,17 +9795,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9820,7 +9820,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M21" s="7" t="inlineStr">
+      <c r="M21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9830,17 +9830,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q21" s="7" t="inlineStr">
+      <c r="O21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9880,12 +9880,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z21" s="7" t="inlineStr">
+      <c r="Y21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9910,7 +9910,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE21" s="7" t="inlineStr">
+      <c r="AE21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9920,7 +9920,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG21" s="7" t="inlineStr">
+      <c r="AG21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9930,7 +9930,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI21" s="7" t="inlineStr">
+      <c r="AI21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9940,7 +9940,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK21" s="7" t="inlineStr">
+      <c r="AK21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9960,12 +9960,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP21" s="7" t="inlineStr">
+      <c r="AO21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9985,12 +9985,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU21" s="7" t="inlineStr">
+      <c r="AT21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10030,42 +10030,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ21" s="7" t="inlineStr">
+      <c r="BC21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10107,9 +10107,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -10122,17 +10122,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J22" s="7" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10147,7 +10147,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M22" s="7" t="inlineStr">
+      <c r="M22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10157,29 +10157,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T22" s="6" t="inlineStr">
@@ -10207,12 +10207,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z22" s="7" t="inlineStr">
+      <c r="Y22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10237,7 +10237,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE22" s="7" t="inlineStr">
+      <c r="AE22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10247,7 +10247,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG22" s="7" t="inlineStr">
+      <c r="AG22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10257,7 +10257,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI22" s="7" t="inlineStr">
+      <c r="AI22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10267,7 +10267,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK22" s="7" t="inlineStr">
+      <c r="AK22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10287,7 +10287,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO22" s="7" t="inlineStr">
+      <c r="AO22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10312,12 +10312,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU22" s="7" t="inlineStr">
+      <c r="AT22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10327,19 +10327,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ22" s="6" t="inlineStr">
@@ -10357,42 +10357,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ22" s="7" t="inlineStr">
+      <c r="BC22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10407,9 +10407,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -10434,7 +10434,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -10449,17 +10449,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10474,7 +10474,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M23" s="7" t="inlineStr">
+      <c r="M23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10484,17 +10484,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q23" s="7" t="inlineStr">
+      <c r="O23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10534,12 +10534,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z23" s="7" t="inlineStr">
+      <c r="Y23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10564,7 +10564,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE23" s="7" t="inlineStr">
+      <c r="AE23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10574,7 +10574,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG23" s="7" t="inlineStr">
+      <c r="AG23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10584,7 +10584,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI23" s="7" t="inlineStr">
+      <c r="AI23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10594,7 +10594,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK23" s="7" t="inlineStr">
+      <c r="AK23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10639,12 +10639,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU23" s="7" t="inlineStr">
+      <c r="AT23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10684,42 +10684,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ23" s="7" t="inlineStr">
+      <c r="BC23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10761,7 +10761,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -10776,17 +10776,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J24" s="7" t="inlineStr">
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10801,7 +10801,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M24" s="7" t="inlineStr">
+      <c r="M24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10811,17 +10811,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q24" s="7" t="inlineStr">
+      <c r="O24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10861,12 +10861,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z24" s="7" t="inlineStr">
+      <c r="Y24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10891,7 +10891,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE24" s="7" t="inlineStr">
+      <c r="AE24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10901,7 +10901,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG24" s="7" t="inlineStr">
+      <c r="AG24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10911,7 +10911,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI24" s="7" t="inlineStr">
+      <c r="AI24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10921,7 +10921,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK24" s="7" t="inlineStr">
+      <c r="AK24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10941,12 +10941,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP24" s="7" t="inlineStr">
+      <c r="AO24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10966,12 +10966,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU24" s="7" t="inlineStr">
+      <c r="AT24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11011,42 +11011,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ24" s="7" t="inlineStr">
+      <c r="BC24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11088,7 +11088,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -11103,17 +11103,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J25" s="7" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11128,7 +11128,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M25" s="7" t="inlineStr">
+      <c r="M25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11138,17 +11138,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q25" s="7" t="inlineStr">
+      <c r="O25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11188,12 +11188,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z25" s="7" t="inlineStr">
+      <c r="Y25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11218,7 +11218,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE25" s="7" t="inlineStr">
+      <c r="AE25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11228,7 +11228,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG25" s="7" t="inlineStr">
+      <c r="AG25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11238,7 +11238,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI25" s="7" t="inlineStr">
+      <c r="AI25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11248,7 +11248,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK25" s="7" t="inlineStr">
+      <c r="AK25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11293,12 +11293,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU25" s="7" t="inlineStr">
+      <c r="AT25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11338,42 +11338,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ25" s="7" t="inlineStr">
+      <c r="BC25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11415,9 +11415,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -11430,17 +11430,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J26" s="7" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11455,7 +11455,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M26" s="7" t="inlineStr">
+      <c r="M26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11465,29 +11465,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R26" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S26" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T26" s="6" t="inlineStr">
@@ -11515,12 +11515,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z26" s="7" t="inlineStr">
+      <c r="Y26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11545,7 +11545,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE26" s="7" t="inlineStr">
+      <c r="AE26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11555,7 +11555,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG26" s="7" t="inlineStr">
+      <c r="AG26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11565,7 +11565,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI26" s="7" t="inlineStr">
+      <c r="AI26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11575,7 +11575,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK26" s="7" t="inlineStr">
+      <c r="AK26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11595,7 +11595,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO26" s="7" t="inlineStr">
+      <c r="AO26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11620,12 +11620,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU26" s="7" t="inlineStr">
+      <c r="AT26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11635,19 +11635,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW26" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX26" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY26" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ26" s="6" t="inlineStr">
@@ -11665,42 +11665,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ26" s="7" t="inlineStr">
+      <c r="BC26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11715,9 +11715,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -11742,7 +11742,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -11757,17 +11757,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J27" s="7" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11782,7 +11782,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M27" s="7" t="inlineStr">
+      <c r="M27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11792,17 +11792,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q27" s="7" t="inlineStr">
+      <c r="O27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11842,12 +11842,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z27" s="7" t="inlineStr">
+      <c r="Y27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11872,7 +11872,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE27" s="7" t="inlineStr">
+      <c r="AE27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11882,7 +11882,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG27" s="7" t="inlineStr">
+      <c r="AG27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11892,7 +11892,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI27" s="7" t="inlineStr">
+      <c r="AI27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11902,7 +11902,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK27" s="7" t="inlineStr">
+      <c r="AK27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11922,12 +11922,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP27" s="7" t="inlineStr">
+      <c r="AO27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11947,12 +11947,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU27" s="7" t="inlineStr">
+      <c r="AT27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11992,42 +11992,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ27" s="7" t="inlineStr">
+      <c r="BC27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12063,7 +12063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12097,7 +12097,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>STM32U595ZJ</t>
+          <t>STM32U5A5VJ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -12112,14 +12112,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STM32U595ZJ</t>
+          <t>STM32U5A5VJ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -12134,14 +12134,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STM32U595ZJ</t>
+          <t>STM32U5A5VJ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -12156,14 +12156,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STM32U595ZJ</t>
+          <t>STM32U5A5VJ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -12178,14 +12178,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STM32U595ZJ</t>
+          <t>STM32U5A5VJ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -12200,14 +12200,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+          <t>Table 65. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STM32U595QJ</t>
+          <t>STM32U595ZJ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -12229,7 +12229,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STM32U595QJ</t>
+          <t>STM32U595ZJ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -12251,7 +12251,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM32U595QJ</t>
+          <t>STM32U595ZJ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -12273,7 +12273,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM32U595QJ</t>
+          <t>STM32U595ZJ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -12295,7 +12295,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32U595QJ</t>
+          <t>STM32U595ZJ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -12317,7 +12317,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STM32U595QI</t>
+          <t>STM32U595QJ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -12339,7 +12339,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32U595QI</t>
+          <t>STM32U595QJ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -12361,7 +12361,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32U595QI</t>
+          <t>STM32U595QJ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -12383,7 +12383,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32U595QI</t>
+          <t>STM32U595QJ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -12405,7 +12405,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32U595QI</t>
+          <t>STM32U595QJ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -12427,7 +12427,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32U595VI</t>
+          <t>STM32U5A5QJ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -12442,14 +12442,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32U595VI</t>
+          <t>STM32U5A5QJ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -12464,14 +12464,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32U595VI</t>
+          <t>STM32U5A5QJ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -12486,14 +12486,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32U595VI</t>
+          <t>STM32U5A5QJ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -12508,14 +12508,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32U595VI</t>
+          <t>STM32U5A5QJ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -12530,14 +12530,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+          <t>Table 65. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32U595RI</t>
+          <t>STM32U595QI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -12559,7 +12559,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32U595RI</t>
+          <t>STM32U595QI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -12581,7 +12581,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32U595RI</t>
+          <t>STM32U595QI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -12603,7 +12603,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32U595RI</t>
+          <t>STM32U595QI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -12625,7 +12625,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32U595RI</t>
+          <t>STM32U595QI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -12647,7 +12647,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32U595VJ</t>
+          <t>STM32U595VI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -12669,7 +12669,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32U595VJ</t>
+          <t>STM32U595VI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12691,7 +12691,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32U595VJ</t>
+          <t>STM32U595VI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12713,7 +12713,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32U595VJ</t>
+          <t>STM32U595VI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -12735,7 +12735,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32U595VJ</t>
+          <t>STM32U595VI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -12757,7 +12757,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32U595AI</t>
+          <t>STM32U595RI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -12779,7 +12779,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32U595AI</t>
+          <t>STM32U595RI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -12801,7 +12801,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32U595AI</t>
+          <t>STM32U595RI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -12823,7 +12823,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32U595AI</t>
+          <t>STM32U595RI</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -12845,7 +12845,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32U595AI</t>
+          <t>STM32U595RI</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -12867,7 +12867,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32U595ZI</t>
+          <t>STM32U595VJ</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -12889,7 +12889,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32U595ZI</t>
+          <t>STM32U595VJ</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -12911,7 +12911,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32U595ZI</t>
+          <t>STM32U595VJ</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -12933,7 +12933,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32U595ZI</t>
+          <t>STM32U595VJ</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -12955,7 +12955,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32U595ZI</t>
+          <t>STM32U595VJ</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -12977,7 +12977,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32U595RJ</t>
+          <t>STM32U5A5ZJ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -12992,14 +12992,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32U595RJ</t>
+          <t>STM32U5A5ZJ</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -13014,14 +13014,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32U595RJ</t>
+          <t>STM32U5A5ZJ</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -13036,14 +13036,14 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32U595RJ</t>
+          <t>STM32U5A5ZJ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -13058,14 +13058,14 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32U595RJ</t>
+          <t>STM32U5A5ZJ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -13080,14 +13080,14 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+          <t>Table 65. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32U5A5AJ</t>
+          <t>STM32U595AI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -13102,14 +13102,14 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32U5A5AJ</t>
+          <t>STM32U595AI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -13124,14 +13124,14 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32U5A5AJ</t>
+          <t>STM32U595AI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -13146,14 +13146,14 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32U5A5AJ</t>
+          <t>STM32U595AI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -13168,14 +13168,14 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32U5A5AJ</t>
+          <t>STM32U595AI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -13190,14 +13190,14 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Table 65. Typical dynamic current consumption of peripherals</t>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32U595AJ</t>
+          <t>STM32U5A5QI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -13212,14 +13212,14 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32U595AJ</t>
+          <t>STM32U5A5QI</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -13234,14 +13234,14 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32U595AJ</t>
+          <t>STM32U5A5QI</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -13256,14 +13256,14 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32U595AJ</t>
+          <t>STM32U5A5QI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -13278,27 +13278,577 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>STM32U5A5QI</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Table 65. Typical dynamic current consumption of peripherals</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>STM32U595ZI</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>STM32U595ZI</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>STM32U595ZI</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>STM32U595ZI</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>STM32U595ZI</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>STM32U595RJ</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>STM32U595RJ</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>STM32U595RJ</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>STM32U595RJ</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>STM32U595RJ</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Table 64. Typical dynamic current consumption of peripherals</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>STM32U5A5AJ</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>STM32U5A5AJ</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>STM32U5A5AJ</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>STM32U5A5AJ</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>STM32U5A5AJ</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Table 65. Typical dynamic current consumption of peripherals</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>STM32U5A5RJ</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>STM32U5A5RJ</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Table 20. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>STM32U5A5RJ</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>STM32U5A5RJ</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>STM32U5A5RJ</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Table 65. Typical dynamic current consumption of peripherals</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
           <t>STM32U595AJ</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>STM32U595AJ</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>STM32U595AJ</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>STM32U595AJ</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>STM32U595AJ</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
         <is>
           <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
         <is>
           <t>Table 64. Typical dynamic current consumption of peripherals</t>
         </is>

--- a/product_selector_out/STM32U595-5A5.xlsx
+++ b/product_selector_out/STM32U595-5A5.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM27"/>
+  <dimension ref="A1:BN27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.34375" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -895,6 +896,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -990,6 +996,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1314,6 +1321,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
         </is>
       </c>
@@ -1641,6 +1653,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u595ai.pdf</t>
         </is>
       </c>
@@ -1968,6 +1985,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u595ai.pdf</t>
         </is>
       </c>
@@ -2295,6 +2317,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
         </is>
       </c>
@@ -2622,6 +2649,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u595ai.pdf</t>
         </is>
       </c>
@@ -2949,6 +2981,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u595ai.pdf</t>
         </is>
       </c>
@@ -3276,6 +3313,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u595ai.pdf</t>
         </is>
       </c>
@@ -3603,6 +3645,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u595ai.pdf</t>
         </is>
       </c>
@@ -3930,6 +3977,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
         </is>
       </c>
@@ -4257,6 +4309,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u595ai.pdf</t>
         </is>
       </c>
@@ -4584,6 +4641,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
         </is>
       </c>
@@ -4911,6 +4973,11 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u595ai.pdf</t>
         </is>
       </c>
@@ -5238,6 +5305,11 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u595ai.pdf</t>
         </is>
       </c>
@@ -5565,6 +5637,11 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
         </is>
       </c>
@@ -5892,6 +5969,11 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5a5aj.pdf</t>
         </is>
       </c>
@@ -6219,12 +6301,17 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u595ai.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -6245,16 +6332,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -6267,6 +6352,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -6286,7 +6372,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -6319,7 +6407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM27"/>
+  <dimension ref="A1:BN27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6387,6 +6475,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6720,6 +6809,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -6815,6 +6909,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -7137,7 +7232,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7464,7 +7564,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7791,7 +7896,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8118,7 +8228,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8445,7 +8560,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8772,7 +8892,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9099,7 +9224,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9426,7 +9556,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9753,7 +9888,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10080,7 +10220,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10407,7 +10552,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10734,7 +10884,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11061,7 +11216,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
+      <c r="BM24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11388,7 +11548,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
+      <c r="BM25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11715,7 +11880,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
+      <c r="BM26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12042,7 +12212,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
+      <c r="BM27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12050,8 +12225,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
